--- a/src/data/downloads/October_8,_2016_elections_to_the_Supreme_Council_of_the_Auto_runoff_20161008_data_2026-04-28T13-04-37.xlsx
+++ b/src/data/downloads/October_8,_2016_elections_to_the_Supreme_Council_of_the_Auto_runoff_20161008_data_2026-04-28T13-04-37.xlsx
@@ -1161,13 +1161,13 @@
     <t>Archive</t>
   </si>
   <si>
-    <t>Comprehensive Election Data Archive of Georgia (CEDAG)</t>
+    <t>Georgia Election Data Archive (GEDA)</t>
   </si>
   <si>
     <t>Website</t>
   </si>
   <si>
-    <t>https://electionsdata.ge</t>
+    <t>https://electionsdata.ge/elections?type=adjara&amp;election=adj_2016&amp;sub=adj_2016_smd_runoff</t>
   </si>
   <si>
     <t>Author</t>
@@ -1194,12 +1194,6 @@
     <t>adj_2016</t>
   </si>
   <si>
-    <t>Sub-election ID</t>
-  </si>
-  <si>
-    <t>adj_2016_smd_runoff</t>
-  </si>
-  <si>
     <t>Election Type</t>
   </si>
   <si>
@@ -1215,7 +1209,7 @@
     <t>File Generated</t>
   </si>
   <si>
-    <t>2026-04-28T13:04:37.294Z</t>
+    <t>2026-04-30T18:50:28.616Z</t>
   </si>
   <si>
     <t>Data Source</t>
@@ -1224,10 +1218,16 @@
     <t>Public information requested from the Supreme Electoral Council of Adjara</t>
   </si>
   <si>
+    <t>Citation (APA)</t>
+  </si>
+  <si>
+    <t>Sichinava, D. (2026). Results of the October 8, 2016 elections to the Supreme Council of the Autonomous Republic of Adjara - Second Round (October 30, 2016). Georgia Election Data Archive (GEDA). https://electionsdata.ge/elections?type=adjara&amp;election=adj_2016&amp;sub=adj_2016_smd_runoff</t>
+  </si>
+  <si>
     <t>License</t>
   </si>
   <si>
-    <t>Open data. Please cite CEDAG when using.</t>
+    <t>CC-BY-4.0</t>
   </si>
 </sst>
 </file>
@@ -2414,7 +2414,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -37191,7 +37191,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
